--- a/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
+++ b/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:48+00:00</t>
+    <t>2024-02-05T18:23:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
+++ b/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:23:38+00:00</t>
+    <t>2024-02-07T08:22:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
+++ b/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T08:22:38+00:00</t>
+    <t>2024-02-08T15:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
+++ b/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:43:07+00:00</t>
+    <t>2024-02-08T15:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
+++ b/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:45:12+00:00</t>
+    <t>2024-02-16T10:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
+++ b/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:46:50+00:00</t>
+    <t>2024-02-16T10:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
+++ b/ig/main/StructureDefinition-as-ext-lieu-dit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:57:00+00:00</t>
+    <t>2024-02-16T18:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
